--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118276435</v>
+        <v>118276720</v>
       </c>
       <c r="B2" t="n">
-        <v>43659</v>
+        <v>94620</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gömmaren (Gömmaren), Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666011</v>
+        <v>665925</v>
       </c>
       <c r="R2" t="n">
-        <v>6571139</v>
+        <v>6571151</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118276720</v>
+        <v>118276435</v>
       </c>
       <c r="B3" t="n">
-        <v>94620</v>
+        <v>43659</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,37 +803,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gömmaren (Gömmaren), Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665925</v>
+        <v>666011</v>
       </c>
       <c r="R3" t="n">
-        <v>6571151</v>
+        <v>6571139</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,6 +890,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118276720</v>
+        <v>118276435</v>
       </c>
       <c r="B2" t="n">
-        <v>94620</v>
+        <v>43659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gömmaren (Gömmaren), Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665925</v>
+        <v>666011</v>
       </c>
       <c r="R2" t="n">
-        <v>6571151</v>
+        <v>6571139</v>
       </c>
       <c r="S2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +778,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118276435</v>
+        <v>118276275</v>
       </c>
       <c r="B3" t="n">
-        <v>43659</v>
+        <v>8405</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666011</v>
+        <v>665947</v>
       </c>
       <c r="R3" t="n">
-        <v>6571139</v>
+        <v>6571129</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118276275</v>
+        <v>118276720</v>
       </c>
       <c r="B4" t="n">
-        <v>8405</v>
+        <v>94620</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,43 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gömmaren (Gömmaren), Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665947</v>
+        <v>665925</v>
       </c>
       <c r="R4" t="n">
-        <v>6571129</v>
+        <v>6571151</v>
       </c>
       <c r="S4" t="n">
         <v>40</v>
@@ -993,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1013,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,6 +1029,108 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121409016</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92008</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gömmaren, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>665965</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6571116</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>121409016</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>121409016</v>
       </c>
       <c r="B5" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>121409016</v>
       </c>
       <c r="B5" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>121409016</v>
       </c>
       <c r="B5" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>121409016</v>
       </c>
       <c r="B5" t="n">
-        <v>92030</v>
+        <v>92031</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118276435</v>
+        <v>131457352</v>
       </c>
       <c r="B2" t="n">
-        <v>43659</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gömmaren (Gömmaren), Srm</t>
+          <t>Gömmarens naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666011</v>
+        <v>665902</v>
       </c>
       <c r="R2" t="n">
-        <v>6571139</v>
+        <v>6571163</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,74 +764,63 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118276275</v>
+        <v>131457095</v>
       </c>
       <c r="B3" t="n">
-        <v>8405</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gömmaren (Gömmaren), Srm</t>
+          <t>Gömmarens naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665947</v>
+        <v>666044</v>
       </c>
       <c r="R3" t="n">
-        <v>6571129</v>
+        <v>6571179</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,12 +865,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -922,12 +880,7 @@
         <v>118276720</v>
       </c>
       <c r="B4" t="n">
-        <v>94620</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,7 +908,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gömmaren (Gömmaren), Srm</t>
+          <t>Gömmaren, Gömmaren, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1031,50 +984,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121409016</v>
+        <v>131457330</v>
       </c>
       <c r="B5" t="n">
-        <v>92039</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gömmaren, Srm</t>
+          <t>Gömmarens naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665965</v>
+        <v>665924</v>
       </c>
       <c r="R5" t="n">
-        <v>6571116</v>
+        <v>6571196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,12 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,21 +1066,1092 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131457068</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>666036</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6571141</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121409016</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gömmaren, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>665965</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6571116</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131457081</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>666026</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6571157</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131457334</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>665924</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6571196</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131457349</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>665902</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6571163</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131457338</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>665924</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6571196</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118276435</v>
+      </c>
+      <c r="B12" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gömmaren, Gömmaren, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>666011</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6571139</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131457100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>666041</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6571179</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131457356</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>665903</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6571164</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118276275</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gömmaren, Gömmaren, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>665947</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6571129</v>
+      </c>
+      <c r="S15" t="n">
+        <v>40</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24365-2023 artfynd.xlsx
+++ b/artfynd/A 24365-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457352</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457095</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118276720</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457330</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457068</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121409016</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457081</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457334</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457349</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457338</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,6 +1888,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118276435</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2035,6 +2100,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457356</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2152,8 +2222,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118276275</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>